--- a/settlements/grove/2026-08/grove_settlement_august_2026.xlsx
+++ b/settlements/grove/2026-08/grove_settlement_august_2026.xlsx
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3723114.746746849</v>
+        <v>3720604.844326282</v>
       </c>
     </row>
     <row r="11">
@@ -555,7 +555,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>8342320.790779008</v>
+        <v>8339810.88835844</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>3723114.746746849</v>
+        <v>3720604.844326282</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-4853702.318594626</v>
+        <v>-4856212.221015193</v>
       </c>
     </row>
     <row r="17">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-3723114.746746849</v>
+        <v>-3720604.844326282</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" s="4" t="n">
-        <v>4715579.368145472</v>
+        <v>4718089.27056604</v>
       </c>
     </row>
     <row r="24">
@@ -666,7 +666,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01T15:43:37+00:00</t>
+          <t>2026-09-01T22:20:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1001,13 +1001,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>1070395.004891111</v>
+        <v>1069673.408272021</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>1070395.004891111</v>
+        <v>1069673.408272021</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>72663.28247590478</v>
+        <v>73384.87909499553</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1066,13 +1066,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>838766.3333419418</v>
+        <v>838200.8869902857</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>838766.3333419418</v>
+        <v>838200.8869902857</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-98593.72664477673</v>
+        <v>-98028.28029312054</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1131,13 +1131,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>534371.2152415023</v>
+        <v>534010.9739656221</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>534371.2152415023</v>
+        <v>534010.9739656221</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>36275.54910351604</v>
+        <v>36635.79037939616</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1196,13 +1196,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>421212.7128356218</v>
+        <v>420928.7562886355</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>421212.7128356218</v>
+        <v>420928.7562886355</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>48062.38716437824</v>
+        <v>48346.3437113645</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1261,13 +1261,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>348633.5937432529</v>
+        <v>348398.5657195821</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>348633.5937432529</v>
+        <v>348398.5657195821</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-41675.55299856862</v>
+        <v>-41440.52497489788</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1326,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>113254.3405028374</v>
+        <v>113177.9911656014</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>113254.3405028374</v>
+        <v>113177.9911656014</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>109681.9294971626</v>
+        <v>109758.2788343986</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>102868.9180695457</v>
+        <v>102799.569966136</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>102868.9180695457</v>
+        <v>102799.569966136</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>3847422.976642454</v>
+        <v>3847492.324745864</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1456,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>99330.84693230143</v>
+        <v>99263.8839859216</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>99330.84693230143</v>
+        <v>99263.8839859216</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-99165.55593495329</v>
+        <v>-99098.59298857345</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1521,13 +1521,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>99089.06830117755</v>
+        <v>99022.26834756394</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>99089.06830117755</v>
+        <v>99022.26834756394</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>34280.38549580349</v>
+        <v>34347.18544941711</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1586,13 +1586,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>51316.97883949883</v>
+        <v>51282.383985951</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>51316.97883949883</v>
+        <v>51282.383985951</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-51316.97883949883</v>
+        <v>-51282.383985951</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1651,13 +1651,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>34435.81842052974</v>
+        <v>34412.60384083315</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>34435.81842052974</v>
+        <v>34412.60384083315</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>2097.662365989765</v>
+        <v>2120.876945686356</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1716,13 +1716,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>9284.836675415005</v>
+        <v>9278.577391017026</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>9284.836675415005</v>
+        <v>9278.577391017026</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-1961.912122159604</v>
+        <v>-1955.652837761625</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1781,13 +1781,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>113.7406112932232</v>
+        <v>113.6639341411555</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>113.7406112932232</v>
+        <v>113.6639341411555</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>-113.7406112932232</v>
+        <v>-113.6639341411555</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1846,13 +1846,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>41.33676595004347</v>
+        <v>41.30889916215919</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>41.33676595004347</v>
+        <v>41.30889916215919</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-41.33676595004347</v>
+        <v>-41.30889916215919</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1911,13 +1911,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0.001516347262318165</v>
+        <v>0.001515325031223236</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>0.001516347262318165</v>
+        <v>0.001515325031223236</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-0.0006405592990834049</v>
+        <v>-0.000639537067988476</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1976,13 +1976,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>5.851906057081565e-05</v>
+        <v>5.847961050232008e-05</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>5.851906057081565e-05</v>
+        <v>5.847961050232008e-05</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-4.197332796988065e-05</v>
+        <v>-4.193387790138508e-05</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2041,13 +2041,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>4.105358307159906e-09</v>
+        <v>4.10259071887608e-09</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>4.105358307159906e-09</v>
+        <v>4.10259071887608e-09</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-4.105358307159906e-09</v>
+        <v>-4.10259071887608e-09</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1200841730.804709</v>
+        <v>1200035278.799186</v>
       </c>
     </row>
     <row r="6">
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>200841730.8047092</v>
+        <v>200035278.7991856</v>
       </c>
     </row>
     <row r="8">
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.03650495523808599</v>
+        <v>0.03650486142207407</v>
       </c>
     </row>
     <row r="12">
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>-1.396022618230493</v>
+        <v>-1.396960778349715</v>
       </c>
     </row>
     <row r="13">
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>3737352.683385389</v>
+        <v>3734842.780964822</v>
       </c>
     </row>
     <row r="16">
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3723114.746746849</v>
+        <v>3720604.844326282</v>
       </c>
     </row>
     <row r="17">
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>200841730.8047092</v>
+        <v>200035278.7991856</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>625075.1970917451</v>
+        <v>622565.2946711777</v>
       </c>
     </row>
     <row r="23">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3723114.746746849</v>
+        <v>3720604.844326282</v>
       </c>
     </row>
     <row r="25">
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>8342320.790779008</v>
+        <v>8339810.88835844</v>
       </c>
     </row>
     <row r="28">
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>3723114.746746849</v>
+        <v>3720604.844326282</v>
       </c>
     </row>
     <row r="32">
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-4853702.318594626</v>
+        <v>-4856212.221015193</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -5124,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>1476321436.881409</v>
+        <v>1501321449.05264</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>0</v>
@@ -5133,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>1225320645.429638</v>
+        <v>1200320633.258407</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0.03519999850777533</v>
@@ -5151,7 +5151,7 @@
         <v>0.03664455749990904</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>123017.3502664987</v>
+        <v>120507.4478459313</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>271234.1880258113</v>
@@ -5176,7 +5176,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" s="10" t="n">
-        <v>3723114.746746849</v>
+        <v>3720604.844326282</v>
       </c>
       <c r="O38" s="10" t="n">
         <v>8576817.065341476</v>

--- a/settlements/grove/2026-08/grove_settlement_august_2026.xlsx
+++ b/settlements/grove/2026-08/grove_settlement_august_2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -507,176 +507,186 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>+ distribution_rewards (settle-dr-dune)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>16620.77</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>+ chronicle_points (20% of base rate on Chronicle Farm USDS)</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B7" s="3" t="n">
         <v>12218.71084277804</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" s="4" t="n">
-        <v>8529233.784350727</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" s="4" t="n">
+        <v>8545854.554350726</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>3720604.844326282</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>3720604.844326282</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B12" s="3" t="n">
         <v>4619206.044032157</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" s="4" t="n">
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" s="4" t="n">
         <v>8339810.88835844</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>3720604.844326282</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>3720604.844326282</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B17" s="3" t="n">
         <v>-4856212.221015193</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" s="4" t="n">
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" s="4" t="n">
         <v>8576817.065341476</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>8438694.114892321</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>8438694.114892321</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B22" s="3" t="n">
         <v>-3720604.844326282</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" s="4" t="n">
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" s="4" t="n">
         <v>4718089.27056604</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-08-01 → 2026-08-31 (31 days)</t>
-        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>avalanche_c=94159927, base=50715726, ethereum=25878704, monad=100893400, plume=90704090</t>
+          <t>2026-08-01 → 2026-08-31 (31 days)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01T22:20:57+00:00</t>
+          <t>avalanche_c=94159927, base=50715726, ethereum=25878704, monad=100893400, plume=90704090</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-09-01T22:20:57+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>

--- a/settlements/grove/2026-08/grove_settlement_august_2026.xlsx
+++ b/settlements/grove/2026-08/grove_settlement_august_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8438694.114892321</v>
+        <v>4438694.114893322</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" s="4" t="n">
-        <v>8545854.554350726</v>
+        <v>4545854.554351727</v>
       </c>
     </row>
     <row r="10">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>8438694.114892321</v>
+        <v>4438694.114893322</v>
       </c>
     </row>
     <row r="22">
@@ -641,7 +641,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>4718089.27056604</v>
+        <v>718089.2705670395</v>
       </c>
     </row>
     <row r="25">
@@ -676,7 +676,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01T22:20:57+00:00</t>
+          <t>2026-09-02T00:02:22+00:00</t>
         </is>
       </c>
     </row>
@@ -1011,13 +1011,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>1069673.408272021</v>
+        <v>1067850.207374846</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>1069673.408272021</v>
+        <v>1067850.207374846</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>73384.87909499553</v>
+        <v>75208.07999216969</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1076,13 +1076,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>838200.8869902857</v>
+        <v>836772.2185786426</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>838200.8869902857</v>
+        <v>836772.2185786426</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-98028.28029312054</v>
+        <v>-96599.61188147742</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1141,13 +1141,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>534010.9739656221</v>
+        <v>533100.7809297798</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>534010.9739656221</v>
+        <v>533100.7809297798</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>36635.79037939616</v>
+        <v>37545.98341523853</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1206,13 +1206,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>420928.7562886355</v>
+        <v>420211.3058218135</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>420928.7562886355</v>
+        <v>420211.3058218135</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>48346.3437113645</v>
+        <v>49063.79417818651</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1271,13 +1271,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>348398.5657195821</v>
+        <v>347804.7390686792</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>348398.5657195821</v>
+        <v>347804.7390686792</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-41440.52497489788</v>
+        <v>-40846.69832399492</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1336,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>113177.9911656014</v>
+        <v>112985.0853558114</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>113177.9911656014</v>
+        <v>112985.0853558114</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>109758.2788343986</v>
+        <v>109951.1846441886</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1383,31 +1383,31 @@
         <v>3950291.894712</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>3950291.894712</v>
+        <v>-49708.105287</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>3950291.894712</v>
+        <v>-49708.105287</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>25057232.614785</v>
+        <v>26605619.71155881</v>
       </c>
       <c r="M10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>102799.569966136</v>
+        <v>108965.9248282898</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>102799.569966136</v>
+        <v>108965.9248282898</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>3847492.324745864</v>
+        <v>-158674.0301152898</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>99263.8839859216</v>
+        <v>99094.69402481704</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>99263.8839859216</v>
+        <v>99094.69402481704</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-99098.59298857345</v>
+        <v>-98929.40302746888</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>99022.26834756394</v>
+        <v>98853.49020734341</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>99022.26834756394</v>
+        <v>98853.49020734341</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>34347.18544941711</v>
+        <v>34515.96358963763</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>51282.383985951</v>
+        <v>51194.97591562844</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>51282.383985951</v>
+        <v>51194.97591562844</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-51282.383985951</v>
+        <v>-51194.97591562844</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1661,13 +1661,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>34412.60384083315</v>
+        <v>34353.94940508527</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>34412.60384083315</v>
+        <v>34353.94940508527</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>2120.876945686356</v>
+        <v>2179.531381434235</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1726,13 +1726,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>9278.577391017026</v>
+        <v>9262.762553990153</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>9278.577391017026</v>
+        <v>9262.762553990153</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-1955.652837761625</v>
+        <v>-1939.838000734752</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1791,13 +1791,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>113.6639341411555</v>
+        <v>113.4702000676524</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>113.6639341411555</v>
+        <v>113.4702000676524</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>-113.6639341411555</v>
+        <v>-113.4702000676524</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1856,13 +1856,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>41.30889916215919</v>
+        <v>41.23849036127538</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>41.30889916215919</v>
+        <v>41.23849036127538</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-41.30889916215919</v>
+        <v>-41.23849036127538</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1921,13 +1921,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0.001515325031223236</v>
+        <v>0.001512742241060302</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>0.001515325031223236</v>
+        <v>0.001512742241060302</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-0.000639537067988476</v>
+        <v>-0.0006369542778255423</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>5.847961050232008e-05</v>
+        <v>5.837993514579564e-05</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>5.847961050232008e-05</v>
+        <v>5.837993514579564e-05</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-4.193387790138508e-05</v>
+        <v>-4.183420254486064e-05</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2051,13 +2051,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>4.10259071887608e-09</v>
+        <v>4.095598073250275e-09</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>4.10259071887608e-09</v>
+        <v>4.095598073250275e-09</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-4.10259071887608e-09</v>
+        <v>-4.095598073250275e-09</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>

--- a/settlements/grove/2026-08/grove_settlement_august_2026.xlsx
+++ b/settlements/grove/2026-08/grove_settlement_august_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4438694.114893322</v>
+        <v>4913183.004893322</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" s="4" t="n">
-        <v>4545854.554351727</v>
+        <v>5020343.444351727</v>
       </c>
     </row>
     <row r="10">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>4438694.114893322</v>
+        <v>4913183.004893322</v>
       </c>
     </row>
     <row r="22">
@@ -641,7 +641,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>718089.2705670395</v>
+        <v>1192578.160567039</v>
       </c>
     </row>
     <row r="25">
@@ -676,7 +676,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02T00:02:22+00:00</t>
+          <t>2026-09-02T01:08:48+00:00</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:S35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -965,59 +965,59 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E20</t>
+          <t>E42</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy AAA CLO (JAAA-avalanche)</t>
+          <t>Galaxy Warehouse (off-chain facility — cash distribution to Grove Eth ALM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>260731201.713697</v>
+        <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>261874260.001064</v>
+        <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1143058.287367016</v>
+        <v>0</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>1143058.287367016</v>
+        <v>474488.89</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>1143058.287367016</v>
+        <v>474488.89</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>260731201.713697</v>
+        <v>304000001</v>
       </c>
       <c r="M4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>1067850.207374846</v>
+        <v>932882.3997984963</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>1067850.207374846</v>
+        <v>932882.3997984963</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>75208.07999216969</v>
+        <v>-458393.5097984963</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1025,64 +1025,68 @@
       <c r="R4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>(off-chain notional)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E23</t>
+          <t>E20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Steakhouse Prime Instant (Base, Morpho V2)</t>
+          <t>Janus Henderson Anemoy AAA CLO (JAAA-avalanche)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>204310140.6956612</v>
+        <v>260731201.713697</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>205050313.3023583</v>
+        <v>261874260.001064</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>740172.6066971652</v>
+        <v>1143058.287367016</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>740172.6066971652</v>
+        <v>1143058.287367016</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>740172.6066971652</v>
+        <v>1143058.287367016</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>204310140.6956612</v>
+        <v>260731201.713697</v>
       </c>
       <c r="M5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>836772.2185786426</v>
+        <v>800103.7774898543</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>836772.2185786426</v>
+        <v>800103.7774898543</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-96599.61188147742</v>
+        <v>342954.5098771617</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1095,59 +1099,59 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E8</t>
+          <t>E23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy AAA CLO (JAAA)</t>
+          <t>Steakhouse Prime Instant (Base, Morpho V2)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>130164330.4336038</v>
+        <v>204310140.6956612</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>130734977.1979488</v>
+        <v>205050313.3023583</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>570646.7643450183</v>
+        <v>740172.6066971652</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>570646.7643450183</v>
+        <v>740172.6066971652</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>570646.7643450183</v>
+        <v>740172.6066971652</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>130164330.4336038</v>
+        <v>204310140.6956612</v>
       </c>
       <c r="M6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>533100.7809297798</v>
+        <v>626964.9135801707</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>533100.7809297798</v>
+        <v>626964.9135801707</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>37545.98341523853</v>
+        <v>113207.6931169944</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1160,12 +1164,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>E8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Securitize Tokenized AAA CLO Fund (STAC)</t>
+          <t>Janus Henderson Anemoy AAA CLO (JAAA)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1179,40 +1183,40 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>102600718.7</v>
+        <v>130164330.4336038</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>103069993.8</v>
+        <v>130734977.1979488</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>469275.1</v>
+        <v>570646.7643450183</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>469275.1</v>
+        <v>570646.7643450183</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>469275.1</v>
+        <v>570646.7643450183</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>102600718.7</v>
+        <v>130164330.4336038</v>
       </c>
       <c r="M7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>420211.3058218135</v>
+        <v>399434.2517882582</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>420211.3058218135</v>
+        <v>399434.2517882582</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>49063.79417818651</v>
+        <v>171212.5125567601</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1225,59 +1229,59 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E19</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC High Yield (Base, Morpho 4626)</t>
+          <t>Securitize Tokenized AAA CLO Fund (STAC)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>74985592.29829088</v>
+        <v>102600718.7</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>78292572.65257983</v>
+        <v>103069993.8</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>3306980.354288955</v>
+        <v>469275.1</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>306958.0407446842</v>
+        <v>469275.1</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>306958.0407446842</v>
+        <v>469275.1</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>84921599.44607566</v>
+        <v>102600718.7</v>
       </c>
       <c r="M8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>347804.7390686792</v>
+        <v>314850.0143653172</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>347804.7390686792</v>
+        <v>314850.0143653172</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-40846.69832399492</v>
+        <v>154425.0856346827</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1290,59 +1294,59 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E21</t>
+          <t>E19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Galaxy Arch CLO Token (GACLO-1)</t>
+          <t>Grove x Steakhouse USDC High Yield (Base, Morpho 4626)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>27586956.37</v>
+        <v>74985592.29829088</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>17907834.79</v>
+        <v>78292572.65257983</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-9679121.58</v>
+        <v>3306980.354288955</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>222936.27</v>
+        <v>306958.0407446842</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>222936.27</v>
+        <v>306958.0407446842</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>27586956.37</v>
+        <v>84921599.44607566</v>
       </c>
       <c r="M9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>112985.0853558114</v>
+        <v>260598.240872972</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>112985.0853558114</v>
+        <v>260598.240872972</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>109951.1846441886</v>
+        <v>46359.79987171225</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1355,59 +1359,59 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E12</t>
+          <t>E21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions)</t>
+          <t>Galaxy Arch CLO Token (GACLO-1)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>25057232.614785</v>
+        <v>27586956.37</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>29007524.509497</v>
+        <v>17907834.79</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>3950291.894712</v>
+        <v>-9679121.58</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-49708.105287</v>
+        <v>222936.27</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>-49708.105287</v>
+        <v>222936.27</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>26605619.71155881</v>
+        <v>27586956.37</v>
       </c>
       <c r="M10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>108965.9248282898</v>
+        <v>84655.87492409915</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>108965.9248282898</v>
+        <v>84655.87492409915</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>-158674.0301152898</v>
+        <v>138280.3950759009</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1420,12 +1424,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E11</t>
+          <t>E12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Curve AUSD/USDC stableswap LP</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1439,40 +1443,40 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>25001934.08299074</v>
+        <v>25057232.614785</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0</v>
+        <v>29007524.509497</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-25001934.08299074</v>
+        <v>3950291.894712</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>165.2909973481477</v>
+        <v>-49708.105287</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>165.2909973481477</v>
+        <v>-49708.105287</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>24195414.74834597</v>
+        <v>26605619.71155881</v>
       </c>
       <c r="M11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>99094.69402481704</v>
+        <v>81644.45487829178</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>99094.69402481704</v>
+        <v>81644.45487829178</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-98929.40302746888</v>
+        <v>-131352.5601652918</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1485,59 +1489,59 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E22</t>
+          <t>E11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Anemoy Tokenized Apollo Diversified Credit Fund (ACRDX)</t>
+          <t>Curve AUSD/USDC stableswap LP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>plume</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>32853651.7342501</v>
+        <v>25001934.08299074</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>20703791.96596751</v>
+        <v>0</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-12149859.76828259</v>
+        <v>-25001934.08299074</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>133369.453796981</v>
+        <v>165.2909973481477</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>133369.453796981</v>
+        <v>165.2909973481477</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>24136521.31858072</v>
+        <v>24195414.74834597</v>
       </c>
       <c r="M12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>98853.49020734341</v>
+        <v>74248.27796154158</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>98853.49020734341</v>
+        <v>74248.27796154158</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>34515.96358963763</v>
+        <v>-74082.98696419342</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1550,59 +1554,59 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E41</t>
+          <t>E22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JTRSY Basin escrow — USDS pending subscription (Diamond PAU)</t>
+          <t>Anemoy Tokenized Apollo Diversified Credit Fund (ACRDX)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>plume</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1000000</v>
+        <v>32853651.7342501</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>12500000</v>
+        <v>20703791.96596751</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>11500000</v>
+        <v>-12149859.76828259</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0</v>
+        <v>133369.453796981</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0</v>
+        <v>133369.453796981</v>
       </c>
       <c r="K13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>12500000</v>
+        <v>24136521.31858072</v>
       </c>
       <c r="M13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>51194.97591562844</v>
+        <v>74067.55215920263</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>51194.97591562844</v>
+        <v>74067.55215920263</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-51194.97591562844</v>
+        <v>59301.90163777841</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1615,12 +1619,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>E41</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse AUSD (Morpho 4626)</t>
+          <t>JTRSY Basin escrow — USDS pending subscription (Diamond PAU)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1630,44 +1634,44 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>25197943.54576933</v>
+        <v>1000000</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.02838475959697621</v>
+        <v>12500000</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-25197943.51738457</v>
+        <v>11500000</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>36533.48078651951</v>
+        <v>0</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>36533.48078651951</v>
+        <v>0</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>8388017.767041751</v>
+        <v>12500000</v>
       </c>
       <c r="M14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>34353.94940508527</v>
+        <v>38358.65118132419</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>34353.94940508527</v>
+        <v>38358.65118132419</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>2179.531381434235</v>
+        <v>-38358.65118132419</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1680,12 +1684,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC (Morpho 4626)</t>
+          <t>Grove x Steakhouse AUSD (Morpho 4626)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1699,40 +1703,40 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1003527.316199909</v>
+        <v>25197943.54576933</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>4010961.682987081</v>
+        <v>0.02838475959697621</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>3007434.366787171</v>
+        <v>-25197943.51738457</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>7322.9245532554</v>
+        <v>36533.48078651951</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>7322.9245532554</v>
+        <v>36533.48078651951</v>
       </c>
       <c r="K15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>2261638.566168971</v>
+        <v>8388017.767041751</v>
       </c>
       <c r="M15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>9262.762553990153</v>
+        <v>25740.24381029635</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>9262.762553990153</v>
+        <v>25740.24381029635</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-1939.838000734752</v>
+        <v>10793.23697622316</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1745,12 +1749,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E15</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Grove x Steakhouse USDC (Morpho 4626)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1760,44 +1764,44 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>1003527.316199909</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>999.178498</v>
+        <v>4010961.682987081</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>999.178498</v>
+        <v>3007434.366787171</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-1.4e-23</v>
+        <v>7322.9245532554</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-1.4e-23</v>
+        <v>7322.9245532554</v>
       </c>
       <c r="K16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>27705.40420183423</v>
+        <v>2261638.566168971</v>
       </c>
       <c r="M16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>113.4702000676524</v>
+        <v>6940.272388632459</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>113.4702000676524</v>
+        <v>6940.272388632459</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>-113.4702000676524</v>
+        <v>382.6521646229415</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1810,12 +1814,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E31</t>
+          <t>E15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AUSD raw (alt holder idle)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1829,40 +1833,40 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>10068.978846</v>
+        <v>0</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>10068.978846</v>
+        <v>999.178498</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0</v>
+        <v>999.178498</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0</v>
+        <v>-1.4e-23</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0</v>
+        <v>-1.4e-23</v>
       </c>
       <c r="K17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>10068.978846</v>
+        <v>27705.40420183423</v>
       </c>
       <c r="M17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>41.23849036127538</v>
+        <v>85.01935484926022</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>41.23849036127538</v>
+        <v>85.01935484926022</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-41.23849036127538</v>
+        <v>-85.01935484926022</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1875,12 +1879,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aave Ethereum RLUSD (aToken)</t>
+          <t>AUSD raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1890,44 +1894,44 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.369358080066628</v>
+        <v>10068.978846</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.3702338680298627</v>
+        <v>10068.978846</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.00087578796323476</v>
+        <v>0</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.00087578796323476</v>
+        <v>0</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.00087578796323476</v>
+        <v>0</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0.369358080066628</v>
+        <v>10068.978846</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0.001512742241060302</v>
+        <v>30.89859578446769</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>0.001512742241060302</v>
+        <v>30.89859578446769</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-0.0006369542778255423</v>
+        <v>-30.89859578446769</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1940,12 +1944,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aave Horizon RWA RLUSD (aToken)</t>
+          <t>Aave Ethereum RLUSD (aToken)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1959,40 +1963,40 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.01425431258186553</v>
+        <v>0.369358080066628</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.01427085831446647</v>
+        <v>0.3702338680298627</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1.6545732600935e-05</v>
+        <v>0.00087578796323476</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>1.6545732600935e-05</v>
+        <v>0.00087578796323476</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>1.6545732600935e-05</v>
+        <v>0.00087578796323476</v>
       </c>
       <c r="K19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.01425431258186553</v>
+        <v>0.369358080066628</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>5.837993514579564e-05</v>
+        <v>0.001133446220342351</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>5.837993514579564e-05</v>
+        <v>0.001133446220342351</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-4.183420254486064e-05</v>
+        <v>-0.0002576582571075914</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2005,12 +2009,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aave Horizon RWA USDC (aToken)</t>
+          <t>Aave Horizon RWA RLUSD (aToken)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2024,40 +2028,40 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.01425431258186553</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.01427085831446647</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0</v>
+        <v>1.6545732600935e-05</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0</v>
+        <v>1.6545732600935e-05</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0</v>
+        <v>1.6545732600935e-05</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.01425431258186553</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>4.095598073250275e-09</v>
+        <v>4.374209633258725e-05</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>4.095598073250275e-09</v>
+        <v>4.374209633258725e-05</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-4.095598073250275e-09</v>
+        <v>-2.719636373165225e-05</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2070,12 +2074,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
+          <t>Aave Horizon RWA USDC (aToken)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2085,14 +2089,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
@@ -2110,19 +2114,19 @@
         <v>0</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="M21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0</v>
+        <v>3.068692094505935e-09</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>0</v>
+        <v>3.068692094505935e-09</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0</v>
+        <v>-3.068692094505935e-09</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
@@ -2135,12 +2139,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E37</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
+          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2200,12 +2204,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E30</t>
+          <t>E37</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2215,7 +2219,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
@@ -2265,12 +2269,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RLUSD raw (ALM idle)</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2280,7 +2284,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
@@ -2330,12 +2334,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E32</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDC raw (alt holder idle)</t>
+          <t>RLUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2395,12 +2399,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E16</t>
+          <t>E32</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>USDC raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2460,12 +2464,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2503,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="5" t="n">
         <v>0</v>
@@ -2520,21 +2524,17 @@
       <c r="R27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>E17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
@@ -2572,7 +2572,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>0</v>
@@ -2589,17 +2589,21 @@
       <c r="R28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>E24</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
+          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2659,12 +2663,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>E26</t>
+          <t>E24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PYUSD raw (ALM idle)</t>
+          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2674,7 +2678,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
@@ -2724,17 +2728,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>E27</t>
+          <t>E26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>USDC raw on Base (ALM idle)</t>
+          <t>PYUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2789,17 +2793,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>E38</t>
+          <t>E27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Agora AUSD incentives (cash distribution to Grove Eth ALM)</t>
+          <t>USDC raw on Base (ALM idle)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2817,13 +2821,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>857964</v>
+        <v>0</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>857964</v>
+        <v>0</v>
       </c>
       <c r="K32" s="5" t="n">
         <v>0</v>
@@ -2841,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>857964</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="5" t="n">
         <v>0</v>
@@ -2854,12 +2858,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>E40</t>
+          <t>E38</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>USDS raw (Diamond PAU ALM idle)</t>
+          <t>Agora AUSD incentives (cash distribution to Grove Eth ALM)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2882,13 +2886,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>0</v>
+        <v>857964</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>0</v>
+        <v>857964</v>
       </c>
       <c r="K33" s="5" t="n">
         <v>0</v>
@@ -2906,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>0</v>
+        <v>857964</v>
       </c>
       <c r="Q33" s="5" t="n">
         <v>0</v>
@@ -2915,6 +2919,132 @@
         <v>0</v>
       </c>
       <c r="S33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>E40</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>USDS raw (Diamond PAU ALM idle)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PSM_CURVE_DEDUCT</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/settlements/grove/2026-08/grove_settlement_august_2026.xlsx
+++ b/settlements/grove/2026-08/grove_settlement_august_2026.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02T01:08:48+00:00</t>
+          <t>2026-09-02T03:04:03+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-08/grove_settlement_august_2026.xlsx
+++ b/settlements/grove/2026-08/grove_settlement_august_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4438694.114893322</v>
+        <v>4913183.004893322</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" s="4" t="n">
-        <v>4545854.554351727</v>
+        <v>5020343.444351727</v>
       </c>
     </row>
     <row r="10">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>4438694.114893322</v>
+        <v>4913183.004893322</v>
       </c>
     </row>
     <row r="22">
@@ -641,7 +641,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>718089.2705670395</v>
+        <v>1192578.160567039</v>
       </c>
     </row>
     <row r="25">
@@ -676,7 +676,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02T00:02:22+00:00</t>
+          <t>2026-09-02T03:04:03+00:00</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:S35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -965,59 +965,59 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E20</t>
+          <t>E42</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy AAA CLO (JAAA-avalanche)</t>
+          <t>Galaxy Warehouse (off-chain facility — cash distribution to Grove Eth ALM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>260731201.713697</v>
+        <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>261874260.001064</v>
+        <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1143058.287367016</v>
+        <v>0</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>1143058.287367016</v>
+        <v>474488.89</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>1143058.287367016</v>
+        <v>474488.89</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>260731201.713697</v>
+        <v>304000001</v>
       </c>
       <c r="M4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>1067850.207374846</v>
+        <v>932882.3997984963</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>1067850.207374846</v>
+        <v>932882.3997984963</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>75208.07999216969</v>
+        <v>-458393.5097984963</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1025,64 +1025,68 @@
       <c r="R4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>(off-chain notional)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E23</t>
+          <t>E20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Steakhouse Prime Instant (Base, Morpho V2)</t>
+          <t>Janus Henderson Anemoy AAA CLO (JAAA-avalanche)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>204310140.6956612</v>
+        <v>260731201.713697</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>205050313.3023583</v>
+        <v>261874260.001064</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>740172.6066971652</v>
+        <v>1143058.287367016</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>740172.6066971652</v>
+        <v>1143058.287367016</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>740172.6066971652</v>
+        <v>1143058.287367016</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>204310140.6956612</v>
+        <v>260731201.713697</v>
       </c>
       <c r="M5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>836772.2185786426</v>
+        <v>800103.7774898543</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>836772.2185786426</v>
+        <v>800103.7774898543</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-96599.61188147742</v>
+        <v>342954.5098771617</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1095,59 +1099,59 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E8</t>
+          <t>E23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy AAA CLO (JAAA)</t>
+          <t>Steakhouse Prime Instant (Base, Morpho V2)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>130164330.4336038</v>
+        <v>204310140.6956612</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>130734977.1979488</v>
+        <v>205050313.3023583</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>570646.7643450183</v>
+        <v>740172.6066971652</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>570646.7643450183</v>
+        <v>740172.6066971652</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>570646.7643450183</v>
+        <v>740172.6066971652</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>130164330.4336038</v>
+        <v>204310140.6956612</v>
       </c>
       <c r="M6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>533100.7809297798</v>
+        <v>626964.9135801707</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>533100.7809297798</v>
+        <v>626964.9135801707</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>37545.98341523853</v>
+        <v>113207.6931169944</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1160,12 +1164,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>E8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Securitize Tokenized AAA CLO Fund (STAC)</t>
+          <t>Janus Henderson Anemoy AAA CLO (JAAA)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1179,40 +1183,40 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>102600718.7</v>
+        <v>130164330.4336038</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>103069993.8</v>
+        <v>130734977.1979488</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>469275.1</v>
+        <v>570646.7643450183</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>469275.1</v>
+        <v>570646.7643450183</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>469275.1</v>
+        <v>570646.7643450183</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>102600718.7</v>
+        <v>130164330.4336038</v>
       </c>
       <c r="M7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>420211.3058218135</v>
+        <v>399434.2517882582</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>420211.3058218135</v>
+        <v>399434.2517882582</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>49063.79417818651</v>
+        <v>171212.5125567601</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1225,59 +1229,59 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E19</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC High Yield (Base, Morpho 4626)</t>
+          <t>Securitize Tokenized AAA CLO Fund (STAC)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>74985592.29829088</v>
+        <v>102600718.7</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>78292572.65257983</v>
+        <v>103069993.8</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>3306980.354288955</v>
+        <v>469275.1</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>306958.0407446842</v>
+        <v>469275.1</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>306958.0407446842</v>
+        <v>469275.1</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>84921599.44607566</v>
+        <v>102600718.7</v>
       </c>
       <c r="M8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>347804.7390686792</v>
+        <v>314850.0143653172</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>347804.7390686792</v>
+        <v>314850.0143653172</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-40846.69832399492</v>
+        <v>154425.0856346827</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1290,59 +1294,59 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E21</t>
+          <t>E19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Galaxy Arch CLO Token (GACLO-1)</t>
+          <t>Grove x Steakhouse USDC High Yield (Base, Morpho 4626)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>27586956.37</v>
+        <v>74985592.29829088</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>17907834.79</v>
+        <v>78292572.65257983</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-9679121.58</v>
+        <v>3306980.354288955</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>222936.27</v>
+        <v>306958.0407446842</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>222936.27</v>
+        <v>306958.0407446842</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>27586956.37</v>
+        <v>84921599.44607566</v>
       </c>
       <c r="M9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>112985.0853558114</v>
+        <v>260598.240872972</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>112985.0853558114</v>
+        <v>260598.240872972</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>109951.1846441886</v>
+        <v>46359.79987171225</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1355,59 +1359,59 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E12</t>
+          <t>E21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions)</t>
+          <t>Galaxy Arch CLO Token (GACLO-1)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>25057232.614785</v>
+        <v>27586956.37</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>29007524.509497</v>
+        <v>17907834.79</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>3950291.894712</v>
+        <v>-9679121.58</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-49708.105287</v>
+        <v>222936.27</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>-49708.105287</v>
+        <v>222936.27</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>26605619.71155881</v>
+        <v>27586956.37</v>
       </c>
       <c r="M10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>108965.9248282898</v>
+        <v>84655.87492409915</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>108965.9248282898</v>
+        <v>84655.87492409915</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>-158674.0301152898</v>
+        <v>138280.3950759009</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1420,12 +1424,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E11</t>
+          <t>E12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Curve AUSD/USDC stableswap LP</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1439,40 +1443,40 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>25001934.08299074</v>
+        <v>25057232.614785</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0</v>
+        <v>29007524.509497</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-25001934.08299074</v>
+        <v>3950291.894712</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>165.2909973481477</v>
+        <v>-49708.105287</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>165.2909973481477</v>
+        <v>-49708.105287</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>24195414.74834597</v>
+        <v>26605619.71155881</v>
       </c>
       <c r="M11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>99094.69402481704</v>
+        <v>81644.45487829178</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>99094.69402481704</v>
+        <v>81644.45487829178</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-98929.40302746888</v>
+        <v>-131352.5601652918</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1485,59 +1489,59 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E22</t>
+          <t>E11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Anemoy Tokenized Apollo Diversified Credit Fund (ACRDX)</t>
+          <t>Curve AUSD/USDC stableswap LP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>plume</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>32853651.7342501</v>
+        <v>25001934.08299074</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>20703791.96596751</v>
+        <v>0</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-12149859.76828259</v>
+        <v>-25001934.08299074</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>133369.453796981</v>
+        <v>165.2909973481477</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>133369.453796981</v>
+        <v>165.2909973481477</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>24136521.31858072</v>
+        <v>24195414.74834597</v>
       </c>
       <c r="M12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>98853.49020734341</v>
+        <v>74248.27796154158</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>98853.49020734341</v>
+        <v>74248.27796154158</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>34515.96358963763</v>
+        <v>-74082.98696419342</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1550,59 +1554,59 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E41</t>
+          <t>E22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JTRSY Basin escrow — USDS pending subscription (Diamond PAU)</t>
+          <t>Anemoy Tokenized Apollo Diversified Credit Fund (ACRDX)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>plume</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1000000</v>
+        <v>32853651.7342501</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>12500000</v>
+        <v>20703791.96596751</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>11500000</v>
+        <v>-12149859.76828259</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0</v>
+        <v>133369.453796981</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0</v>
+        <v>133369.453796981</v>
       </c>
       <c r="K13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>12500000</v>
+        <v>24136521.31858072</v>
       </c>
       <c r="M13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>51194.97591562844</v>
+        <v>74067.55215920263</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>51194.97591562844</v>
+        <v>74067.55215920263</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-51194.97591562844</v>
+        <v>59301.90163777841</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1615,12 +1619,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>E41</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse AUSD (Morpho 4626)</t>
+          <t>JTRSY Basin escrow — USDS pending subscription (Diamond PAU)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1630,44 +1634,44 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>25197943.54576933</v>
+        <v>1000000</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.02838475959697621</v>
+        <v>12500000</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-25197943.51738457</v>
+        <v>11500000</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>36533.48078651951</v>
+        <v>0</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>36533.48078651951</v>
+        <v>0</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>8388017.767041751</v>
+        <v>12500000</v>
       </c>
       <c r="M14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>34353.94940508527</v>
+        <v>38358.65118132419</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>34353.94940508527</v>
+        <v>38358.65118132419</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>2179.531381434235</v>
+        <v>-38358.65118132419</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1680,12 +1684,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC (Morpho 4626)</t>
+          <t>Grove x Steakhouse AUSD (Morpho 4626)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1699,40 +1703,40 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1003527.316199909</v>
+        <v>25197943.54576933</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>4010961.682987081</v>
+        <v>0.02838475959697621</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>3007434.366787171</v>
+        <v>-25197943.51738457</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>7322.9245532554</v>
+        <v>36533.48078651951</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>7322.9245532554</v>
+        <v>36533.48078651951</v>
       </c>
       <c r="K15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>2261638.566168971</v>
+        <v>8388017.767041751</v>
       </c>
       <c r="M15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>9262.762553990153</v>
+        <v>25740.24381029635</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>9262.762553990153</v>
+        <v>25740.24381029635</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-1939.838000734752</v>
+        <v>10793.23697622316</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1745,12 +1749,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E15</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Grove x Steakhouse USDC (Morpho 4626)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1760,44 +1764,44 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>1003527.316199909</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>999.178498</v>
+        <v>4010961.682987081</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>999.178498</v>
+        <v>3007434.366787171</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-1.4e-23</v>
+        <v>7322.9245532554</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-1.4e-23</v>
+        <v>7322.9245532554</v>
       </c>
       <c r="K16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>27705.40420183423</v>
+        <v>2261638.566168971</v>
       </c>
       <c r="M16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>113.4702000676524</v>
+        <v>6940.272388632459</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>113.4702000676524</v>
+        <v>6940.272388632459</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>-113.4702000676524</v>
+        <v>382.6521646229415</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1810,12 +1814,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E31</t>
+          <t>E15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AUSD raw (alt holder idle)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1829,40 +1833,40 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>10068.978846</v>
+        <v>0</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>10068.978846</v>
+        <v>999.178498</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0</v>
+        <v>999.178498</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0</v>
+        <v>-1.4e-23</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0</v>
+        <v>-1.4e-23</v>
       </c>
       <c r="K17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>10068.978846</v>
+        <v>27705.40420183423</v>
       </c>
       <c r="M17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>41.23849036127538</v>
+        <v>85.01935484926022</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>41.23849036127538</v>
+        <v>85.01935484926022</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-41.23849036127538</v>
+        <v>-85.01935484926022</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1875,12 +1879,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aave Ethereum RLUSD (aToken)</t>
+          <t>AUSD raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1890,44 +1894,44 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.369358080066628</v>
+        <v>10068.978846</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.3702338680298627</v>
+        <v>10068.978846</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.00087578796323476</v>
+        <v>0</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.00087578796323476</v>
+        <v>0</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.00087578796323476</v>
+        <v>0</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0.369358080066628</v>
+        <v>10068.978846</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0.001512742241060302</v>
+        <v>30.89859578446769</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>0.001512742241060302</v>
+        <v>30.89859578446769</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-0.0006369542778255423</v>
+        <v>-30.89859578446769</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1940,12 +1944,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aave Horizon RWA RLUSD (aToken)</t>
+          <t>Aave Ethereum RLUSD (aToken)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1959,40 +1963,40 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.01425431258186553</v>
+        <v>0.369358080066628</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.01427085831446647</v>
+        <v>0.3702338680298627</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1.6545732600935e-05</v>
+        <v>0.00087578796323476</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>1.6545732600935e-05</v>
+        <v>0.00087578796323476</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>1.6545732600935e-05</v>
+        <v>0.00087578796323476</v>
       </c>
       <c r="K19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.01425431258186553</v>
+        <v>0.369358080066628</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>5.837993514579564e-05</v>
+        <v>0.001133446220342351</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>5.837993514579564e-05</v>
+        <v>0.001133446220342351</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-4.183420254486064e-05</v>
+        <v>-0.0002576582571075914</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2005,12 +2009,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aave Horizon RWA USDC (aToken)</t>
+          <t>Aave Horizon RWA RLUSD (aToken)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2024,40 +2028,40 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.01425431258186553</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.01427085831446647</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0</v>
+        <v>1.6545732600935e-05</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0</v>
+        <v>1.6545732600935e-05</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0</v>
+        <v>1.6545732600935e-05</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.01425431258186553</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>4.095598073250275e-09</v>
+        <v>4.374209633258725e-05</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>4.095598073250275e-09</v>
+        <v>4.374209633258725e-05</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-4.095598073250275e-09</v>
+        <v>-2.719636373165225e-05</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2070,12 +2074,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
+          <t>Aave Horizon RWA USDC (aToken)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2085,14 +2089,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
@@ -2110,19 +2114,19 @@
         <v>0</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="M21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0</v>
+        <v>3.068692094505935e-09</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>0</v>
+        <v>3.068692094505935e-09</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0</v>
+        <v>-3.068692094505935e-09</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
@@ -2135,12 +2139,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E37</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
+          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2200,12 +2204,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E30</t>
+          <t>E37</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2215,7 +2219,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
@@ -2265,12 +2269,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RLUSD raw (ALM idle)</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2280,7 +2284,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
@@ -2330,12 +2334,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E32</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDC raw (alt holder idle)</t>
+          <t>RLUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2395,12 +2399,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E16</t>
+          <t>E32</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>USDC raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2460,12 +2464,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2503,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="5" t="n">
         <v>0</v>
@@ -2520,21 +2524,17 @@
       <c r="R27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>E17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
@@ -2572,7 +2572,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>0</v>
@@ -2589,17 +2589,21 @@
       <c r="R28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>E24</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
+          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2659,12 +2663,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>E26</t>
+          <t>E24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PYUSD raw (ALM idle)</t>
+          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2674,7 +2678,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
@@ -2724,17 +2728,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>E27</t>
+          <t>E26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>USDC raw on Base (ALM idle)</t>
+          <t>PYUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2789,17 +2793,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>E38</t>
+          <t>E27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Agora AUSD incentives (cash distribution to Grove Eth ALM)</t>
+          <t>USDC raw on Base (ALM idle)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2817,13 +2821,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>857964</v>
+        <v>0</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>857964</v>
+        <v>0</v>
       </c>
       <c r="K32" s="5" t="n">
         <v>0</v>
@@ -2841,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>857964</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="5" t="n">
         <v>0</v>
@@ -2854,12 +2858,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>E40</t>
+          <t>E38</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>USDS raw (Diamond PAU ALM idle)</t>
+          <t>Agora AUSD incentives (cash distribution to Grove Eth ALM)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2882,13 +2886,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>0</v>
+        <v>857964</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>0</v>
+        <v>857964</v>
       </c>
       <c r="K33" s="5" t="n">
         <v>0</v>
@@ -2906,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>0</v>
+        <v>857964</v>
       </c>
       <c r="Q33" s="5" t="n">
         <v>0</v>
@@ -2915,6 +2919,132 @@
         <v>0</v>
       </c>
       <c r="S33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>E40</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>USDS raw (Diamond PAU ALM idle)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PSM_CURVE_DEDUCT</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/settlements/grove/2026-08/grove_settlement_august_2026.xlsx
+++ b/settlements/grove/2026-08/grove_settlement_august_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4913183.004893322</v>
+        <v>4975029.896919321</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" s="4" t="n">
-        <v>5020343.444351727</v>
+        <v>5082190.336377727</v>
       </c>
     </row>
     <row r="10">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>4913183.004893322</v>
+        <v>4975029.896919321</v>
       </c>
     </row>
     <row r="22">
@@ -641,7 +641,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>1192578.160567039</v>
+        <v>1254425.05259304</v>
       </c>
     </row>
     <row r="25">
@@ -676,7 +676,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02T03:04:03+00:00</t>
+          <t>2026-09-02T13:58:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1011,13 +1011,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>932882.3997984963</v>
+        <v>932905.426134183</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>932882.3997984963</v>
+        <v>932905.426134183</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>-458393.5097984963</v>
+        <v>-458416.536134183</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1080,13 +1080,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>800103.7774898543</v>
+        <v>800123.5264508901</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>800103.7774898543</v>
+        <v>800123.5264508901</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>342954.5098771617</v>
+        <v>342934.7609161259</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1145,13 +1145,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>626964.9135801707</v>
+        <v>626980.3889547378</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>626964.9135801707</v>
+        <v>626980.3889547378</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>113207.6931169944</v>
+        <v>113192.2177424274</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1210,13 +1210,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>399434.2517882582</v>
+        <v>399444.1110236435</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>399434.2517882582</v>
+        <v>399444.1110236435</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>171212.5125567601</v>
+        <v>171202.6533213748</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1275,13 +1275,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>314850.0143653172</v>
+        <v>314857.7858080235</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>314850.0143653172</v>
+        <v>314857.7858080235</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>154425.0856346827</v>
+        <v>154417.3141919765</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1340,13 +1340,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>260598.240872972</v>
+        <v>260604.6732191873</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>260598.240872972</v>
+        <v>260604.6732191873</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>46359.79987171225</v>
+        <v>46353.36752549692</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1405,13 +1405,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>84655.87492409915</v>
+        <v>84657.96448500658</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>84655.87492409915</v>
+        <v>84657.96448500658</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>138280.3950759009</v>
+        <v>138278.3055149934</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1452,31 +1452,31 @@
         <v>3950291.894712</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-49708.105287</v>
+        <v>12138.786739</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-49708.105287</v>
+        <v>12138.786739</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>26605619.71155881</v>
+        <v>26575693.79606235</v>
       </c>
       <c r="M11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>81644.45487829178</v>
+        <v>81554.63442129105</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>81644.45487829178</v>
+        <v>81554.63442129105</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-131352.5601652918</v>
+        <v>-69415.84768229105</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1535,13 +1535,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>74248.27796154158</v>
+        <v>74250.11063173974</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>74248.27796154158</v>
+        <v>74250.11063173974</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-74082.98696419342</v>
+        <v>-74084.81963439159</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1600,13 +1600,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>74067.55215920263</v>
+        <v>74069.38036854593</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>74067.55215920263</v>
+        <v>74069.38036854593</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>59301.90163777841</v>
+        <v>59300.07342843512</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1665,13 +1665,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>38358.65118132419</v>
+        <v>38359.59798788714</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>38358.65118132419</v>
+        <v>38359.59798788714</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-38358.65118132419</v>
+        <v>-38359.59798788714</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>25740.24381029635</v>
+        <v>25740.8791567181</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>25740.24381029635</v>
+        <v>25740.8791567181</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>10793.23697622316</v>
+        <v>10792.6016298014</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1795,13 +1795,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>6940.272388632459</v>
+        <v>6940.443695371456</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>6940.272388632459</v>
+        <v>6940.443695371456</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>382.6521646229415</v>
+        <v>382.4808578839442</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1860,13 +1860,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>85.01935484926022</v>
+        <v>85.02145338194242</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>85.01935484926022</v>
+        <v>85.02145338194242</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-85.01935484926022</v>
+        <v>-85.02145338194242</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1925,13 +1925,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>30.89859578446769</v>
+        <v>30.89935845448798</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>30.89859578446769</v>
+        <v>30.89935845448798</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-30.89859578446769</v>
+        <v>-30.89935845448798</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1990,13 +1990,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.001133446220342351</v>
+        <v>0.001133474197194694</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>0.001133446220342351</v>
+        <v>0.001133474197194694</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-0.0002576582571075914</v>
+        <v>-0.0002576862339599341</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2055,13 +2055,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>4.374209633258725e-05</v>
+        <v>4.374317601872348e-05</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>4.374209633258725e-05</v>
+        <v>4.374317601872348e-05</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-2.719636373165225e-05</v>
+        <v>-2.719744341778848e-05</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2120,13 +2120,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>3.068692094505935e-09</v>
+        <v>3.068767839030971e-09</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>3.068692094505935e-09</v>
+        <v>3.068767839030971e-09</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>-3.068692094505935e-09</v>
+        <v>-3.068767839030971e-09</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>

--- a/settlements/grove/2026-08/grove_settlement_august_2026.xlsx
+++ b/settlements/grove/2026-08/grove_settlement_august_2026.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02T13:58:14+00:00</t>
+          <t>2026-09-02T19:50:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1011,13 +1011,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>932905.426134183</v>
+        <v>939858.3303508102</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>932905.426134183</v>
+        <v>939858.3303508102</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>-458416.536134183</v>
+        <v>-465369.4403508102</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1080,13 +1080,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>800123.5264508901</v>
+        <v>806086.8128516736</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>800123.5264508901</v>
+        <v>806086.8128516736</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>342934.7609161259</v>
+        <v>336971.4745153424</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1145,13 +1145,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>626980.3889547378</v>
+        <v>631653.246961546</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>626980.3889547378</v>
+        <v>631653.246961546</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>113192.2177424274</v>
+        <v>108519.3597356191</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1210,13 +1210,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>399444.1110236435</v>
+        <v>402421.150888608</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>399444.1110236435</v>
+        <v>402421.150888608</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>171202.6533213748</v>
+        <v>168225.6134564103</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1275,13 +1275,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>314857.7858080235</v>
+        <v>317204.4074110879</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>314857.7858080235</v>
+        <v>317204.4074110879</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>154417.3141919765</v>
+        <v>152070.692588912</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1340,13 +1340,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>260604.6732191873</v>
+        <v>262546.9486959277</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>260604.6732191873</v>
+        <v>262546.9486959277</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>46353.36752549692</v>
+        <v>44411.09204875655</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1405,13 +1405,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>84657.96448500658</v>
+        <v>85288.91667131556</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>84657.96448500658</v>
+        <v>85288.91667131556</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>138278.3055149934</v>
+        <v>137647.3533286844</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1470,13 +1470,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>81554.63442129105</v>
+        <v>82162.45762144438</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>81554.63442129105</v>
+        <v>82162.45762144438</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-69415.84768229105</v>
+        <v>-70023.67088244438</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1535,13 +1535,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>74250.11063173974</v>
+        <v>74803.49352869183</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>74250.11063173974</v>
+        <v>74803.49352869183</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-74084.81963439159</v>
+        <v>-74638.20253134368</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1600,13 +1600,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>74069.38036854593</v>
+        <v>74621.41629058092</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>74069.38036854593</v>
+        <v>74621.41629058092</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>59300.07342843512</v>
+        <v>58748.03750640013</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1619,12 +1619,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E41</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JTRSY Basin escrow — USDS pending subscription (Diamond PAU)</t>
+          <t>Grove x Steakhouse AUSD (Morpho 4626)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1634,44 +1634,44 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1000000</v>
+        <v>25197943.54576933</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>12500000</v>
+        <v>0.02838475959697621</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>11500000</v>
+        <v>-25197943.51738457</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0</v>
+        <v>36533.48078651951</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0</v>
+        <v>36533.48078651951</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>12500000</v>
+        <v>8388017.767041751</v>
       </c>
       <c r="M14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>38359.59798788714</v>
+        <v>25932.7248274739</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>38359.59798788714</v>
+        <v>25932.7248274739</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-38359.59798788714</v>
+        <v>10600.7559590456</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1684,12 +1684,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>E41</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse AUSD (Morpho 4626)</t>
+          <t>JTRSY Basin escrow — USDS pending subscription (Diamond PAU)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1699,44 +1699,44 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>25197943.54576933</v>
+        <v>1000000</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.02838475959697621</v>
+        <v>12500000</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-25197943.51738457</v>
+        <v>11500000</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>36533.48078651951</v>
+        <v>0</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>36533.48078651951</v>
+        <v>0</v>
       </c>
       <c r="K15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>8388017.767041751</v>
+        <v>3369516.774752</v>
       </c>
       <c r="M15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>25740.8791567181</v>
+        <v>10417.33026180964</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>25740.8791567181</v>
+        <v>10417.33026180964</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>10792.6016298014</v>
+        <v>-10417.33026180964</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1795,13 +1795,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>6940.443695371456</v>
+        <v>6992.170525211838</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>6940.443695371456</v>
+        <v>6992.170525211838</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>382.4808578839442</v>
+        <v>330.7540280435622</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1814,17 +1814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E15</t>
+          <t>E27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>USDC raw on Base (ALM idle)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1836,37 +1836,37 @@
         <v>0</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>999.178498</v>
+        <v>0</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>999.178498</v>
+        <v>0</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-1.4e-23</v>
+        <v>0</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-1.4e-23</v>
+        <v>0</v>
       </c>
       <c r="K17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>27705.40420183423</v>
+        <v>161290.3225806452</v>
       </c>
       <c r="M17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>85.02145338194242</v>
+        <v>498.6514894201883</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>85.02145338194242</v>
+        <v>498.6514894201883</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-85.02145338194242</v>
+        <v>-498.6514894201883</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1879,12 +1879,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E31</t>
+          <t>E15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AUSD raw (alt holder idle)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1898,40 +1898,40 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>10068.978846</v>
+        <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>10068.978846</v>
+        <v>999.178498</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0</v>
+        <v>999.178498</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0</v>
+        <v>-1.4e-23</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0</v>
+        <v>-1.4e-23</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>10068.978846</v>
+        <v>27705.40420183423</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>30.89935845448798</v>
+        <v>85.65511463544451</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>30.89935845448798</v>
+        <v>85.65511463544451</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-30.89935845448798</v>
+        <v>-85.65511463544451</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1944,12 +1944,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aave Ethereum RLUSD (aToken)</t>
+          <t>AUSD raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1959,44 +1959,44 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.369358080066628</v>
+        <v>10068.978846</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.3702338680298627</v>
+        <v>10068.978846</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.00087578796323476</v>
+        <v>0</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0.00087578796323476</v>
+        <v>0</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.00087578796323476</v>
+        <v>0</v>
       </c>
       <c r="K19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.369358080066628</v>
+        <v>10068.978846</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.001133474197194694</v>
+        <v>31.12965005068927</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>0.001133474197194694</v>
+        <v>31.12965005068927</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-0.0002576862339599341</v>
+        <v>-31.12965005068927</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2009,12 +2009,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aave Horizon RWA RLUSD (aToken)</t>
+          <t>Aave Ethereum RLUSD (aToken)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2028,40 +2028,40 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.01425431258186553</v>
+        <v>0.369358080066628</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.01427085831446647</v>
+        <v>0.3702338680298627</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>1.6545732600935e-05</v>
+        <v>0.00087578796323476</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>1.6545732600935e-05</v>
+        <v>0.00087578796323476</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>1.6545732600935e-05</v>
+        <v>0.00087578796323476</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.01425431258186553</v>
+        <v>0.369358080066628</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>4.374317601872348e-05</v>
+        <v>0.001141921931878552</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>4.374317601872348e-05</v>
+        <v>0.001141921931878552</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-2.719744341778848e-05</v>
+        <v>-0.0002661339686437922</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2074,12 +2074,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aave Horizon RWA USDC (aToken)</t>
+          <t>Aave Horizon RWA RLUSD (aToken)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2093,40 +2093,40 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.01425431258186553</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.01427085831446647</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0</v>
+        <v>1.6545732600935e-05</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0</v>
+        <v>1.6545732600935e-05</v>
       </c>
       <c r="I21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0</v>
+        <v>1.6545732600935e-05</v>
       </c>
       <c r="K21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.01425431258186553</v>
       </c>
       <c r="M21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>3.068767839030971e-09</v>
+        <v>4.406919203757071e-05</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>3.068767839030971e-09</v>
+        <v>4.406919203757071e-05</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>-3.068767839030971e-09</v>
+        <v>-2.752345943663571e-05</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
@@ -2139,12 +2139,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
+          <t>Aave Horizon RWA USDC (aToken)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2154,14 +2154,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>0</v>
@@ -2179,19 +2179,19 @@
         <v>0</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="M22" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>0</v>
+        <v>3.091639234405168e-09</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>0</v>
+        <v>3.091639234405168e-09</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0</v>
+        <v>-3.091639234405168e-09</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>0</v>
@@ -2204,12 +2204,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E37</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
+          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2269,12 +2269,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E30</t>
+          <t>E37</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
@@ -2334,12 +2334,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RLUSD raw (ALM idle)</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
@@ -2399,12 +2399,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E32</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDC raw (alt holder idle)</t>
+          <t>RLUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2464,12 +2464,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>E16</t>
+          <t>E32</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>USDC raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2529,12 +2529,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2572,7 +2572,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>0</v>
@@ -2589,21 +2589,17 @@
       <c r="R28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>E17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2613,7 +2609,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
@@ -2641,7 +2637,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" s="5" t="n">
         <v>0</v>
@@ -2658,17 +2654,21 @@
       <c r="R29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>E24</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
+          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2728,12 +2728,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>E26</t>
+          <t>E24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PYUSD raw (ALM idle)</t>
+          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
@@ -2793,17 +2793,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>E27</t>
+          <t>E26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>USDC raw on Base (ALM idle)</t>
+          <t>PYUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">

--- a/settlements/grove/2026-08/grove_settlement_august_2026.xlsx
+++ b/settlements/grove/2026-08/grove_settlement_august_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4975029.896919321</v>
+        <v>4955508.14483875</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" s="4" t="n">
-        <v>5082190.336377727</v>
+        <v>5062668.584297156</v>
       </c>
     </row>
     <row r="10">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>4975029.896919321</v>
+        <v>4955508.14483875</v>
       </c>
     </row>
     <row r="22">
@@ -641,7 +641,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>1254425.05259304</v>
+        <v>1234903.300512468</v>
       </c>
     </row>
     <row r="25">
@@ -676,7 +676,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02T19:50:48+00:00</t>
+          <t>2026-09-02T21:08:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1011,13 +1011,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>939858.3303508102</v>
+        <v>943028.1360796315</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>939858.3303508102</v>
+        <v>943028.1360796315</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>-465369.4403508102</v>
+        <v>-468539.2460796316</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1080,13 +1080,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>806086.8128516736</v>
+        <v>808805.4551350811</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>806086.8128516736</v>
+        <v>808805.4551350811</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>336971.4745153424</v>
+        <v>334252.8322319349</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1145,13 +1145,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>631653.246961546</v>
+        <v>633783.5872651745</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>631653.246961546</v>
+        <v>633783.5872651745</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>108519.3597356191</v>
+        <v>106389.0194319907</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1210,13 +1210,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>402421.150888608</v>
+        <v>403778.3733851193</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>402421.150888608</v>
+        <v>403778.3733851193</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>168225.6134564103</v>
+        <v>166868.3909598991</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1275,13 +1275,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>317204.4074110879</v>
+        <v>318274.2243349256</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>317204.4074110879</v>
+        <v>318274.2243349256</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>152070.692588912</v>
+        <v>151000.8756650744</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1340,13 +1340,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>262546.9486959277</v>
+        <v>263432.4255759914</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>262546.9486959277</v>
+        <v>263432.4255759914</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>44411.09204875655</v>
+        <v>43525.61516869286</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1359,59 +1359,59 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E21</t>
+          <t>E12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Galaxy Arch CLO Token (GACLO-1)</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>27586956.37</v>
+        <v>25057232.614785</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>17907834.79</v>
+        <v>29007524.509497</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-9679121.58</v>
+        <v>3950291.894712</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>222936.27</v>
+        <v>12138.786739</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>222936.27</v>
+        <v>12138.786739</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>27586956.37</v>
+        <v>26575693.79606235</v>
       </c>
       <c r="M10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>85288.91667131556</v>
+        <v>82439.56218119785</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>85288.91667131556</v>
+        <v>82439.56218119785</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>137647.3533286844</v>
+        <v>-70300.77544219786</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1424,12 +1424,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E12</t>
+          <t>E11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions)</t>
+          <t>Curve AUSD/USDC stableswap LP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1443,40 +1443,40 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>25057232.614785</v>
+        <v>25001934.08299074</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>29007524.509497</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>3950291.894712</v>
+        <v>-25001934.08299074</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>12138.786739</v>
+        <v>165.2909973481477</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>12138.786739</v>
+        <v>165.2909973481477</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>26575693.79606235</v>
+        <v>24195414.74834597</v>
       </c>
       <c r="M11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>82162.45762144438</v>
+        <v>75055.77893667943</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>82162.45762144438</v>
+        <v>75055.77893667943</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-70023.67088244438</v>
+        <v>-74890.48793933127</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1489,59 +1489,59 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E11</t>
+          <t>E22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Curve AUSD/USDC stableswap LP</t>
+          <t>Anemoy Tokenized Apollo Diversified Credit Fund (ACRDX)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>plume</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>25001934.08299074</v>
+        <v>32853651.7342501</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0</v>
+        <v>20703791.96596751</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-25001934.08299074</v>
+        <v>-12149859.76828259</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>165.2909973481477</v>
+        <v>113847.7017164101</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>165.2909973481477</v>
+        <v>113847.7017164101</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>24195414.74834597</v>
+        <v>24150375.46521855</v>
       </c>
       <c r="M12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>74803.49352869183</v>
+        <v>74916.06409760608</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>74803.49352869183</v>
+        <v>74916.06409760608</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-74638.20253134368</v>
+        <v>38931.63761880402</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1554,17 +1554,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E22</t>
+          <t>E21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Anemoy Tokenized Apollo Diversified Credit Fund (ACRDX)</t>
+          <t>Galaxy Arch CLO Token (GACLO-1)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>plume</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1573,40 +1573,40 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>32853651.7342501</v>
+        <v>27586956.37</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>20703791.96596751</v>
+        <v>17907834.79</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-12149859.76828259</v>
+        <v>-9679121.58</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>133369.453796981</v>
+        <v>222936.27</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>133369.453796981</v>
+        <v>222936.27</v>
       </c>
       <c r="K13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>24136521.31858072</v>
+        <v>23527969.90096774</v>
       </c>
       <c r="M13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>74621.41629058092</v>
+        <v>72985.32081730908</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>74621.41629058092</v>
+        <v>72985.32081730908</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>58748.03750640013</v>
+        <v>149950.9491826909</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1665,13 +1665,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>25932.7248274739</v>
+        <v>26020.18662577641</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>25932.7248274739</v>
+        <v>26020.18662577641</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>10600.7559590456</v>
+        <v>10513.2941607431</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>10417.33026180964</v>
+        <v>10452.46418793081</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>10417.33026180964</v>
+        <v>10452.46418793081</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-10417.33026180964</v>
+        <v>-10452.46418793081</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1795,13 +1795,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>6992.170525211838</v>
+        <v>7015.752613567047</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>6992.170525211838</v>
+        <v>7015.752613567047</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>330.7540280435622</v>
+        <v>307.1719396883531</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1860,13 +1860,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>498.6514894201883</v>
+        <v>500.3332624032074</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>498.6514894201883</v>
+        <v>500.3332624032074</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-498.6514894201883</v>
+        <v>-500.3332624032074</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1925,13 +1925,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>85.65511463544451</v>
+        <v>85.94399867712016</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>85.65511463544451</v>
+        <v>85.94399867712016</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-85.65511463544451</v>
+        <v>-85.94399867712016</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1990,13 +1990,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>31.12965005068927</v>
+        <v>31.23463921754599</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>31.12965005068927</v>
+        <v>31.23463921754599</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-31.12965005068927</v>
+        <v>-31.23463921754599</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2055,13 +2055,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0.001141921931878552</v>
+        <v>0.001145773225807271</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>0.001141921931878552</v>
+        <v>0.001145773225807271</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-0.0002661339686437922</v>
+        <v>-0.0002699852625725105</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2120,13 +2120,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>4.406919203757071e-05</v>
+        <v>4.421782164787919e-05</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>4.406919203757071e-05</v>
+        <v>4.421782164787919e-05</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>-2.752345943663571e-05</v>
+        <v>-2.767208904694419e-05</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
@@ -2185,13 +2185,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>3.091639234405168e-09</v>
+        <v>3.102066226899886e-09</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>3.091639234405168e-09</v>
+        <v>3.102066226899886e-09</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>-3.091639234405168e-09</v>
+        <v>-3.102066226899886e-09</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>0</v>
